--- a/exports/trend_1d/INDHOTEL_full_report.xlsx
+++ b/exports/trend_1d/INDHOTEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42048</v>
+        <v>42051</v>
       </c>
       <c r="H2" t="n">
-        <v>111.2</v>
+        <v>108.05</v>
       </c>
       <c r="I2" t="n">
         <v>108.5530009512302</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.42</v>
+        <v>-4.21</v>
       </c>
       <c r="L2" t="n">
-        <v>1.99</v>
+        <v>5.19</v>
       </c>
       <c r="M2" t="n">
         <v>1.49</v>
       </c>
       <c r="N2" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="O2" t="n">
         <v>0.36</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42093</v>
+        <v>42094</v>
       </c>
       <c r="H3" t="n">
-        <v>110.95</v>
+        <v>113.35</v>
       </c>
       <c r="I3" t="n">
         <v>112.5259410618201</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.68</v>
+        <v>-4.91</v>
       </c>
       <c r="L3" t="n">
         <v>7.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>17.1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H4" t="n">
-        <v>96.90000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="I4" t="n">
         <v>95.7150070576843</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K4" t="n">
-        <v>-14.51</v>
+        <v>-17.12</v>
       </c>
       <c r="L4" t="n">
-        <v>17.03</v>
+        <v>17.56</v>
       </c>
       <c r="M4" t="n">
         <v>2.1</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.01</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42304</v>
+        <v>42305</v>
       </c>
       <c r="H5" t="n">
-        <v>88.40000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="I5" t="n">
         <v>90.59073008260282</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K5" t="n">
-        <v>5.91</v>
+        <v>2.87</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42411</v>
+        <v>42412</v>
       </c>
       <c r="H6" t="n">
-        <v>103.8</v>
+        <v>99.8</v>
       </c>
       <c r="I6" t="n">
         <v>103.2516493857207</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K6" t="n">
-        <v>13.75</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>6.25</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>14.1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42471</v>
+        <v>42472</v>
       </c>
       <c r="H7" t="n">
-        <v>98.59999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="I7" t="n">
         <v>99.60353106175187</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="L7" t="n">
         <v>3.96</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42668</v>
+        <v>42669</v>
       </c>
       <c r="H8" t="n">
-        <v>121.7</v>
+        <v>116</v>
       </c>
       <c r="I8" t="n">
         <v>118.6675586397735</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K8" t="n">
-        <v>21.09</v>
+        <v>15.42</v>
       </c>
       <c r="L8" t="n">
         <v>3.53</v>
@@ -897,7 +992,7 @@
         <v>1.88</v>
       </c>
       <c r="N8" t="n">
-        <v>4.26</v>
+        <v>4.68</v>
       </c>
       <c r="O8" t="n">
         <v>1.93</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.27</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42752</v>
+        <v>42753</v>
       </c>
       <c r="H9" t="n">
-        <v>99.7</v>
+        <v>103.6</v>
       </c>
       <c r="I9" t="n">
         <v>100.2247294287759</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K9" t="n">
-        <v>14.05</v>
+        <v>10.69</v>
       </c>
       <c r="L9" t="n">
         <v>5.47</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.84</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H10" t="n">
-        <v>128.25</v>
+        <v>124.95</v>
       </c>
       <c r="I10" t="n">
         <v>126.5142134263403</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K10" t="n">
-        <v>23.79</v>
+        <v>20.61</v>
       </c>
       <c r="L10" t="n">
         <v>3.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.77</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43061</v>
+        <v>43062</v>
       </c>
       <c r="H11" t="n">
-        <v>107.6</v>
+        <v>115.1</v>
       </c>
       <c r="I11" t="n">
         <v>113.5015723839172</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K11" t="n">
-        <v>13.89</v>
+        <v>7.88</v>
       </c>
       <c r="L11" t="n">
         <v>6.08</v>
@@ -1068,7 +1199,7 @@
         <v>2.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.83</v>
+        <v>6.97</v>
       </c>
       <c r="O11" t="n">
         <v>-2.57</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.99</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H12" t="n">
-        <v>134.15</v>
+        <v>125.1</v>
       </c>
       <c r="I12" t="n">
         <v>130.8613196774018</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
-        <v>16.55</v>
+        <v>8.69</v>
       </c>
       <c r="L12" t="n">
         <v>6.56</v>
@@ -1125,7 +1268,7 @@
         <v>1.58</v>
       </c>
       <c r="N12" t="n">
-        <v>5.41</v>
+        <v>6.75</v>
       </c>
       <c r="O12" t="n">
         <v>6.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>21.21</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43206</v>
+        <v>43207</v>
       </c>
       <c r="H13" t="n">
-        <v>135.8</v>
+        <v>142.75</v>
       </c>
       <c r="I13" t="n">
         <v>135.8902920768831</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.550000000000001</v>
+        <v>-14.11</v>
       </c>
       <c r="L13" t="n">
-        <v>10.63</v>
+        <v>17.03</v>
       </c>
       <c r="M13" t="n">
         <v>2.04</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>13.02</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H14" t="n">
-        <v>132.2</v>
+        <v>129.15</v>
       </c>
       <c r="I14" t="n">
         <v>130.1612702998907</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.39</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>8.970000000000001</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
         <v>1.35</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.61</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43342</v>
+        <v>43343</v>
       </c>
       <c r="H15" t="n">
-        <v>130.8</v>
+        <v>133.1</v>
       </c>
       <c r="I15" t="n">
         <v>131.2679949895822</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.28</v>
+        <v>-3.06</v>
       </c>
       <c r="L15" t="n">
         <v>8.09</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H16" t="n">
-        <v>120.85</v>
+        <v>119.75</v>
       </c>
       <c r="I16" t="n">
         <v>120.0358210008876</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.03</v>
       </c>
       <c r="L16" t="n">
-        <v>11.12</v>
+        <v>11.38</v>
       </c>
       <c r="M16" t="n">
         <v>1.18</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.98</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H17" t="n">
-        <v>127.25</v>
+        <v>131.6</v>
       </c>
       <c r="I17" t="n">
         <v>129.2100669117894</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.26</v>
+        <v>-9.9</v>
       </c>
       <c r="L17" t="n">
-        <v>9.52</v>
+        <v>10.52</v>
       </c>
       <c r="M17" t="n">
         <v>1.95</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.32</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43489</v>
+        <v>43490</v>
       </c>
       <c r="H18" t="n">
-        <v>131.55</v>
+        <v>129.45</v>
       </c>
       <c r="I18" t="n">
         <v>131.3725519841728</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.04</v>
+        <v>-1.63</v>
       </c>
       <c r="L18" t="n">
         <v>3.42</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H19" t="n">
-        <v>139.8</v>
+        <v>146.45</v>
       </c>
       <c r="I19" t="n">
         <v>141.6813438622875</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K19" t="n">
-        <v>-8</v>
+        <v>-13.13</v>
       </c>
       <c r="L19" t="n">
-        <v>10.85</v>
+        <v>14.06</v>
       </c>
       <c r="M19" t="n">
         <v>4.48</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>10.99</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H20" t="n">
-        <v>142.15</v>
+        <v>138.95</v>
       </c>
       <c r="I20" t="n">
         <v>139.5523477924696</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.94</v>
+        <v>-5.12</v>
       </c>
       <c r="L20" t="n">
-        <v>4.37</v>
+        <v>6.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.21</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.15</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H21" t="n">
-        <v>147</v>
+        <v>152.4</v>
       </c>
       <c r="I21" t="n">
         <v>149.094427718889</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.79</v>
+        <v>-9.68</v>
       </c>
       <c r="L21" t="n">
-        <v>8.130000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="M21" t="n">
         <v>2.68</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.41</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H22" t="n">
-        <v>143.7</v>
+        <v>140.05</v>
       </c>
       <c r="I22" t="n">
         <v>140.5452174140569</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.71</v>
+        <v>-8.1</v>
       </c>
       <c r="L22" t="n">
-        <v>8.140000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>0.91</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="O22" t="n">
         <v>3.67</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.83</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H23" t="n">
-        <v>130.75</v>
+        <v>144.55</v>
       </c>
       <c r="I23" t="n">
         <v>138.6830724510442</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K23" t="n">
-        <v>6.64</v>
+        <v>-3.21</v>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
         <v>3.61</v>
       </c>
       <c r="N23" t="n">
-        <v>7.81</v>
+        <v>10.55</v>
       </c>
       <c r="O23" t="n">
         <v>-2.54</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>15.75</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43837</v>
+        <v>43838</v>
       </c>
       <c r="H24" t="n">
-        <v>136.65</v>
+        <v>135</v>
       </c>
       <c r="I24" t="n">
         <v>136.198583138047</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.47</v>
+        <v>-6.61</v>
       </c>
       <c r="L24" t="n">
         <v>9.1</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H25" t="n">
-        <v>73.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>73.77206860908915</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K25" t="n">
-        <v>45.7</v>
+        <v>39.56</v>
       </c>
       <c r="L25" t="n">
         <v>6.11</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>19.18</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44041</v>
+        <v>44042</v>
       </c>
       <c r="H26" t="n">
-        <v>76.75</v>
+        <v>74.55</v>
       </c>
       <c r="I26" t="n">
         <v>74.68922859907623</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.94</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>8.390000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>6.52</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>12.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44054</v>
+        <v>44055</v>
       </c>
       <c r="H27" t="n">
-        <v>81</v>
+        <v>84.75</v>
       </c>
       <c r="I27" t="n">
         <v>81.86547481293076</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.65</v>
+        <v>-13.68</v>
       </c>
       <c r="L27" t="n">
-        <v>10.33</v>
+        <v>14.29</v>
       </c>
       <c r="M27" t="n">
         <v>1.86</v>
       </c>
       <c r="N27" t="n">
-        <v>3.97</v>
+        <v>4.63</v>
       </c>
       <c r="O27" t="n">
         <v>-2.87</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.88</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H28" t="n">
-        <v>93.05</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>90.73370146812471</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>9.789999999999999</v>
+        <v>6.02</v>
       </c>
       <c r="L28" t="n">
         <v>5.01</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.3</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H29" t="n">
-        <v>96.45</v>
+        <v>110.25</v>
       </c>
       <c r="I29" t="n">
         <v>100.5365492640241</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.35</v>
+        <v>-22.7</v>
       </c>
       <c r="L29" t="n">
-        <v>11.07</v>
+        <v>25.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.45</v>
+        <v>9.07</v>
       </c>
       <c r="N29" t="n">
-        <v>5.12</v>
+        <v>14.31</v>
       </c>
       <c r="O29" t="n">
         <v>-3.44</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.06</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44249</v>
+        <v>44250</v>
       </c>
       <c r="H30" t="n">
-        <v>116.2</v>
+        <v>114.55</v>
       </c>
       <c r="I30" t="n">
         <v>116.1552422287562</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K30" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
         <v>7.66</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.66</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
       <c r="H31" t="n">
-        <v>108.05</v>
+        <v>109.5</v>
       </c>
       <c r="I31" t="n">
         <v>108.0731868824309</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K31" t="n">
-        <v>5.67</v>
+        <v>4.41</v>
       </c>
       <c r="L31" t="n">
         <v>10.56</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>15.68</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H32" t="n">
-        <v>205.55</v>
+        <v>182.05</v>
       </c>
       <c r="I32" t="n">
         <v>191.7320047714712</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K32" t="n">
-        <v>87.72</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>5.25</v>
       </c>
       <c r="M32" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="N32" t="n">
-        <v>4.81</v>
+        <v>11.43</v>
       </c>
       <c r="O32" t="n">
         <v>1.34</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>9</v>
+      </c>
+      <c r="U32" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>22.27</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H33" t="n">
-        <v>197.05</v>
+        <v>208.25</v>
       </c>
       <c r="I33" t="n">
         <v>198.6686527497949</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.24</v>
+        <v>-14.39</v>
       </c>
       <c r="L33" t="n">
-        <v>13.43</v>
+        <v>14.91</v>
       </c>
       <c r="M33" t="n">
         <v>1.58</v>
       </c>
       <c r="N33" t="n">
-        <v>4.49</v>
+        <v>5.68</v>
       </c>
       <c r="O33" t="n">
         <v>-11.43</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>13.29</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H34" t="n">
-        <v>204.8</v>
+        <v>194.3</v>
       </c>
       <c r="I34" t="n">
         <v>195.0954258524433</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.66</v>
+        <v>-6.7</v>
       </c>
       <c r="L34" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>2.73</v>
+        <v>3.81</v>
       </c>
       <c r="N34" t="n">
         <v>5.57</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.83</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44642</v>
+        <v>44643</v>
       </c>
       <c r="H35" t="n">
-        <v>208.75</v>
+        <v>216.1</v>
       </c>
       <c r="I35" t="n">
         <v>212.2034239392502</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.44</v>
+        <v>-11.22</v>
       </c>
       <c r="L35" t="n">
-        <v>10.65</v>
+        <v>13.92</v>
       </c>
       <c r="M35" t="n">
         <v>2.88</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.34</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H36" t="n">
-        <v>230.4</v>
+        <v>225</v>
       </c>
       <c r="I36" t="n">
         <v>226.8952995519658</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K36" t="n">
-        <v>6.62</v>
+        <v>4.12</v>
       </c>
       <c r="L36" t="n">
         <v>2.98</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>16.85</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44746</v>
+        <v>44747</v>
       </c>
       <c r="H37" t="n">
-        <v>232.15</v>
+        <v>236.45</v>
       </c>
       <c r="I37" t="n">
         <v>235.605326752897</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.18</v>
+        <v>-5.09</v>
       </c>
       <c r="L37" t="n">
         <v>6.73</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.02</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44847</v>
+        <v>44848</v>
       </c>
       <c r="H38" t="n">
-        <v>317.15</v>
+        <v>309.75</v>
       </c>
       <c r="I38" t="n">
         <v>310.2193520478053</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K38" t="n">
-        <v>34.13</v>
+        <v>31</v>
       </c>
       <c r="L38" t="n">
         <v>1.82</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>13.58</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H39" t="n">
-        <v>301</v>
+        <v>326.7</v>
       </c>
       <c r="I39" t="n">
         <v>310.749760749291</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K39" t="n">
-        <v>2.82</v>
+        <v>-5.47</v>
       </c>
       <c r="L39" t="n">
         <v>12.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3.04</v>
+        <v>5.65</v>
       </c>
       <c r="N39" t="n">
-        <v>4.96</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>-2.33</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.03</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H40" t="n">
-        <v>404.95</v>
+        <v>395.85</v>
       </c>
       <c r="I40" t="n">
         <v>403.0822438817093</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K40" t="n">
-        <v>23.95</v>
+        <v>21.17</v>
       </c>
       <c r="L40" t="n">
         <v>8.720000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>9</v>
+      </c>
+      <c r="U40" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45240</v>
+        <v>45242</v>
       </c>
       <c r="H41" t="n">
-        <v>409.45</v>
+        <v>411.35</v>
       </c>
       <c r="I41" t="n">
         <v>410.296556270044</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.44</v>
+        <v>-3.92</v>
       </c>
       <c r="L41" t="n">
-        <v>3.6</v>
+        <v>4.46</v>
       </c>
       <c r="M41" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="N41" t="n">
         <v>2.02</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.44</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H42" t="n">
-        <v>571.3</v>
+        <v>566.1</v>
       </c>
       <c r="I42" t="n">
         <v>567.1332273912534</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K42" t="n">
-        <v>38.88</v>
+        <v>37.62</v>
       </c>
       <c r="L42" t="n">
         <v>1.25</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.58</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H43" t="n">
-        <v>589.3</v>
+        <v>613.85</v>
       </c>
       <c r="I43" t="n">
         <v>604.8097066698798</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.1</v>
+        <v>-8.43</v>
       </c>
       <c r="L43" t="n">
-        <v>4.93</v>
+        <v>8.74</v>
       </c>
       <c r="M43" t="n">
         <v>3.52</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45475</v>
+        <v>45476</v>
       </c>
       <c r="H44" t="n">
-        <v>603.7</v>
+        <v>599.8</v>
       </c>
       <c r="I44" t="n">
         <v>600.1775256377337</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.65</v>
+        <v>-2.29</v>
       </c>
       <c r="L44" t="n">
         <v>3.89</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H45" t="n">
-        <v>620.35</v>
+        <v>623.5</v>
       </c>
       <c r="I45" t="n">
         <v>621.889196423523</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.43</v>
+        <v>-3.95</v>
       </c>
       <c r="L45" t="n">
         <v>5.28</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H46" t="n">
-        <v>674.05</v>
+        <v>661.45</v>
       </c>
       <c r="I46" t="n">
         <v>664.7449475704028</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K46" t="n">
-        <v>8.109999999999999</v>
+        <v>6.09</v>
       </c>
       <c r="L46" t="n">
         <v>4.57</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8.66</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="H47" t="n">
-        <v>683.8</v>
+        <v>732.9</v>
       </c>
       <c r="I47" t="n">
         <v>718.7141887789138</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.38</v>
+        <v>-10.8</v>
       </c>
       <c r="L47" t="n">
-        <v>8.16</v>
+        <v>12.31</v>
       </c>
       <c r="M47" t="n">
-        <v>0.99</v>
+        <v>3.83</v>
       </c>
       <c r="N47" t="n">
-        <v>4.84</v>
+        <v>7.18</v>
       </c>
       <c r="O47" t="n">
         <v>-1.87</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.88</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H48" t="n">
-        <v>834.9</v>
+        <v>822.85</v>
       </c>
       <c r="I48" t="n">
         <v>825.8735111630639</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K48" t="n">
-        <v>13.92</v>
+        <v>12.27</v>
       </c>
       <c r="L48" t="n">
         <v>5.36</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H49" t="n">
-        <v>786.25</v>
+        <v>810.6</v>
       </c>
       <c r="I49" t="n">
         <v>793.6462367124341</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K49" t="n">
-        <v>4.45</v>
+        <v>1.49</v>
       </c>
       <c r="L49" t="n">
         <v>2.25</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>10.17</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H50" t="n">
-        <v>799.35</v>
+        <v>751.95</v>
       </c>
       <c r="I50" t="n">
         <v>764.8982356087074</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.39</v>
+        <v>-7.24</v>
       </c>
       <c r="L50" t="n">
-        <v>3.53</v>
+        <v>9.33</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>6.92</v>
       </c>
       <c r="N50" t="n">
-        <v>3.81</v>
+        <v>5.93</v>
       </c>
       <c r="O50" t="n">
         <v>3.1</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>12.45</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H51" t="n">
-        <v>775.15</v>
+        <v>806.8</v>
       </c>
       <c r="I51" t="n">
         <v>776.7384978250744</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.09</v>
+        <v>-7.29</v>
       </c>
       <c r="L51" t="n">
         <v>13.48</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.67</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H52" t="n">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="I52" t="n">
         <v>751.5977300754076</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.79</v>
+        <v>-7.54</v>
       </c>
       <c r="L52" t="n">
-        <v>7.53</v>
+        <v>7.72</v>
       </c>
       <c r="M52" t="n">
         <v>1</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.59</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H53" t="n">
-        <v>731.4</v>
+        <v>735</v>
       </c>
       <c r="I53" t="n">
         <v>734.3180950652934</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K53" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="L53" t="n">
         <v>1.43</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.01</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H54" t="n">
-        <v>715.35</v>
+        <v>704.35</v>
       </c>
       <c r="I54" t="n">
         <v>707.3492546020796</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.67</v>
+        <v>-4.17</v>
       </c>
       <c r="L54" t="n">
-        <v>4.31</v>
+        <v>4.63</v>
       </c>
       <c r="M54" t="n">
         <v>0.88</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H55" t="n">
-        <v>695</v>
+        <v>702.55</v>
       </c>
       <c r="I55" t="n">
         <v>697.3605782341226</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>1.33</v>
+        <v>0.26</v>
       </c>
       <c r="L55" t="n">
         <v>1.31</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H56" t="n">
-        <v>667.05</v>
+        <v>651</v>
       </c>
       <c r="I56" t="n">
         <v>651.5490068357941</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.05</v>
+        <v>-7.34</v>
       </c>
       <c r="L56" t="n">
-        <v>5.34</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>0.89</v>
+        <v>3.26</v>
       </c>
       <c r="N56" t="n">
         <v>3.31</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.01</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H57" t="n">
-        <v>634.95</v>
+        <v>646.4</v>
       </c>
       <c r="I57" t="n">
         <v>641.8865154351626</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K57" t="n">
-        <v>2.47</v>
+        <v>0.71</v>
       </c>
       <c r="L57" t="n">
         <v>1.71</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3750,6 +4445,14 @@
       <c r="Q58" t="n">
         <v>135</v>
       </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8708,7 +9411,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8718,7 +9421,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="7">
@@ -8728,7 +9431,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
@@ -8738,7 +9441,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -8748,7 +9451,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="10">
@@ -8758,7 +9461,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -8768,7 +9471,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -8778,7 +9481,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -8788,7 +9491,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.1</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="14">
@@ -8798,7 +9501,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.52</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
@@ -8808,7 +9511,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.279999999999999</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="16">
@@ -8818,7 +9521,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.76</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="17">
@@ -8828,7 +9531,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>87.72</v>
+        <v>66.26000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -8838,7 +9541,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.6</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="19">
@@ -8848,7 +9551,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.62</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="20">
@@ -8858,7 +9561,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.1</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="21">
@@ -8868,7 +9571,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.03</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="22">
@@ -8878,7 +9581,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -8888,7 +9591,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -8898,7 +9601,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="25">
@@ -8908,7 +9611,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.18</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="26">
@@ -8918,7 +9621,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.82</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="27">
@@ -8928,7 +9631,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.52</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="28">
@@ -8938,7 +9641,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
